--- a/excels/project_table_new.xlsx
+++ b/excels/project_table_new.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Python\EMB\blixt_rp\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E934167C-C9C6-4E9B-BE94-D64AC4210161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F6DBF4-8BF0-4ACE-B5A2-16BA92B81AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="685" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6570" yWindow="2745" windowWidth="28800" windowHeight="17145" tabRatio="685" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Well settings" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="405">
   <si>
     <t>Select Yes or No</t>
   </si>
@@ -1280,6 +1280,15 @@
   </si>
   <si>
     <t>Batzle and Wang' or 'User specified' or "Interpolation"</t>
+  </si>
+  <si>
+    <t>Group A</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Group B</t>
   </si>
 </sst>
 </file>
@@ -2020,13 +2029,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2037,7 +2046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2066,7 +2075,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -2086,7 +2095,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -2100,7 +2109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -2114,7 +2123,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -2128,7 +2137,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -2142,7 +2151,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2162,7 +2171,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -2179,7 +2188,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -2193,7 +2202,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C11" s="21" t="s">
         <v>35</v>
       </c>
@@ -2201,7 +2210,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C12" s="22" t="s">
         <v>37</v>
       </c>
@@ -2209,7 +2218,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C13" s="23" t="s">
         <v>39</v>
       </c>
@@ -2233,13 +2242,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F1" s="7" t="s">
         <v>285</v>
       </c>
@@ -2247,7 +2256,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="8" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" s="8" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>254</v>
       </c>
@@ -2270,7 +2279,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>288</v>
       </c>
@@ -2287,7 +2296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>289</v>
       </c>
@@ -2310,7 +2319,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>291</v>
       </c>
@@ -2327,7 +2336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>292</v>
       </c>
@@ -2344,7 +2353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>293</v>
       </c>
@@ -2361,7 +2370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>294</v>
       </c>
@@ -2378,7 +2387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>295</v>
       </c>
@@ -2395,7 +2404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>296</v>
       </c>
@@ -2412,7 +2421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>297</v>
       </c>
@@ -2429,7 +2438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>298</v>
       </c>
@@ -2446,7 +2455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>299</v>
       </c>
@@ -2463,7 +2472,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>300</v>
       </c>
@@ -2480,7 +2489,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>301</v>
       </c>
@@ -2497,7 +2506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>302</v>
       </c>
@@ -2514,7 +2523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>303</v>
       </c>
@@ -2531,7 +2540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>304</v>
       </c>
@@ -2548,7 +2557,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>305</v>
       </c>
@@ -2565,7 +2574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>306</v>
       </c>
@@ -2582,7 +2591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>307</v>
       </c>
@@ -2599,7 +2608,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>308</v>
       </c>
@@ -2616,7 +2625,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>309</v>
       </c>
@@ -2633,7 +2642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>310</v>
       </c>
@@ -2650,7 +2659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>311</v>
       </c>
@@ -2667,7 +2676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>312</v>
       </c>
@@ -2684,7 +2693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>313</v>
       </c>
@@ -2701,7 +2710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>314</v>
       </c>
@@ -2718,7 +2727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>315</v>
       </c>
@@ -2735,7 +2744,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>316</v>
       </c>
@@ -2752,7 +2761,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>317</v>
       </c>
@@ -2769,7 +2778,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>318</v>
       </c>
@@ -2786,7 +2795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>319</v>
       </c>
@@ -2812,14 +2821,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="10.33203125" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" customWidth="1"/>
+    <col min="2" max="3" width="10.28515625" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2827,7 +2836,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="8" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" s="8" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
@@ -2844,7 +2853,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2861,7 +2870,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
         <v>11</v>
       </c>
@@ -2878,7 +2887,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2895,7 +2904,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="31" t="s">
         <v>11</v>
       </c>
@@ -2912,7 +2921,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2929,7 +2938,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="31" t="s">
         <v>11</v>
       </c>
@@ -2985,9 +2994,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCD9C215-DCD2-40A2-A7D5-172DC530BE0E}">
   <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -3008,7 +3017,7 @@
       </c>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>369</v>
       </c>
@@ -3061,9 +3070,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCC2506-3BD3-4476-A9AA-1673C259914E}">
   <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
         <v>374</v>
@@ -3076,7 +3085,7 @@
       <c r="I1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>370</v>
       </c>
@@ -3122,19 +3131,19 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:Q18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H1" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="6" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="6" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>322</v>
       </c>
@@ -3184,7 +3193,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -3210,7 +3219,7 @@
         <v>127</v>
       </c>
       <c r="I3">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H3)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H3)</f>
         <v>4</v>
       </c>
       <c r="J3" t="s">
@@ -3238,7 +3247,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -3264,7 +3273,7 @@
         <v>146</v>
       </c>
       <c r="I4">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H4)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H4)</f>
         <v>4</v>
       </c>
       <c r="J4" t="s">
@@ -3289,7 +3298,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>398</v>
       </c>
@@ -3306,7 +3315,7 @@
         <v>161</v>
       </c>
       <c r="I5">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H5)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H5)</f>
         <v>4</v>
       </c>
       <c r="L5" t="s">
@@ -3319,7 +3328,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
         <v>273</v>
       </c>
@@ -3333,7 +3342,7 @@
         <v>162</v>
       </c>
       <c r="I6">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H6)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H6)</f>
         <v>4</v>
       </c>
       <c r="O6" t="s">
@@ -3343,7 +3352,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
         <v>397</v>
       </c>
@@ -3354,7 +3363,7 @@
         <v>163</v>
       </c>
       <c r="I7">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H7)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H7)</f>
         <v>4</v>
       </c>
       <c r="O7" t="s">
@@ -3364,7 +3373,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F8" t="s">
         <v>33</v>
       </c>
@@ -3372,11 +3381,11 @@
         <v>164</v>
       </c>
       <c r="I8">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H8)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H8)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F9" t="s">
         <v>24</v>
       </c>
@@ -3384,11 +3393,11 @@
         <v>139</v>
       </c>
       <c r="I9">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H9)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H9)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
         <v>36</v>
       </c>
@@ -3396,11 +3405,11 @@
         <v>165</v>
       </c>
       <c r="I10">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H10)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H10)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
         <v>38</v>
       </c>
@@ -3408,11 +3417,11 @@
         <v>167</v>
       </c>
       <c r="I11">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H11)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H11)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
         <v>40</v>
       </c>
@@ -3420,11 +3429,11 @@
         <v>168</v>
       </c>
       <c r="I12">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H12)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H12)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F13" t="s">
         <v>339</v>
       </c>
@@ -3432,11 +3441,11 @@
         <v>169</v>
       </c>
       <c r="I13">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H13)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H13)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
         <v>340</v>
       </c>
@@ -3444,11 +3453,11 @@
         <v>170</v>
       </c>
       <c r="I14">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H14)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H14)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F15" t="s">
         <v>121</v>
       </c>
@@ -3456,11 +3465,11 @@
         <v>171</v>
       </c>
       <c r="I15">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H15)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H15)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F16" t="s">
         <v>341</v>
       </c>
@@ -3468,25 +3477,25 @@
         <v>172</v>
       </c>
       <c r="I16">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H16)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H16)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H17" s="30" t="s">
         <v>173</v>
       </c>
       <c r="I17">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H17)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H17)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H18" s="30" t="s">
         <v>174</v>
       </c>
       <c r="I18">
-        <f>COUNTIF('Working intervals'!$C$6:$C$100,H18)</f>
+        <f>COUNTIF('Working intervals'!$C$6:$C$102,H18)</f>
         <v>1</v>
       </c>
     </row>
@@ -3499,19 +3508,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.6640625" style="13" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" customWidth="1"/>
-    <col min="4" max="5" width="11.5546875" customWidth="1"/>
+    <col min="1" max="2" width="9.7109375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" customWidth="1"/>
+    <col min="4" max="5" width="11.5703125" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="11" max="11" width="16.109375" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" customWidth="1"/>
     <col min="13" max="13" width="7" customWidth="1"/>
-    <col min="16" max="16" width="6.5546875" customWidth="1"/>
-    <col min="17" max="17" width="4.6640625" customWidth="1"/>
+    <col min="16" max="16" width="6.5703125" customWidth="1"/>
+    <col min="17" max="17" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>41</v>
       </c>
@@ -3519,7 +3528,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>3</v>
       </c>
@@ -3575,7 +3584,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>12</v>
       </c>
@@ -3604,7 +3613,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>12</v>
       </c>
@@ -3621,7 +3630,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
@@ -3647,7 +3656,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>18</v>
       </c>
@@ -3673,7 +3682,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>22</v>
       </c>
@@ -3702,7 +3711,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>25</v>
       </c>
@@ -3719,7 +3728,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>25</v>
       </c>
@@ -3742,7 +3751,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>28</v>
       </c>
@@ -3774,7 +3783,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>31</v>
       </c>
@@ -3831,13 +3840,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{725EDE5F-2F74-4F10-B375-EE1EEF8AD52D}">
   <dimension ref="A1:M20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>41</v>
       </c>
@@ -3851,7 +3860,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>3</v>
       </c>
@@ -3888,7 +3897,7 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>12</v>
       </c>
@@ -3914,7 +3923,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>12</v>
       </c>
@@ -3937,11 +3946,11 @@
         <v>382</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="13"/>
       <c r="C5" s="4"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>15</v>
       </c>
@@ -3967,7 +3976,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>15</v>
       </c>
@@ -3990,11 +3999,11 @@
         <v>382</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="C8" s="4"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>18</v>
       </c>
@@ -4020,7 +4029,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>18</v>
       </c>
@@ -4043,11 +4052,11 @@
         <v>382</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>22</v>
       </c>
@@ -4056,11 +4065,11 @@
       </c>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>25</v>
       </c>
@@ -4069,7 +4078,7 @@
       </c>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>25</v>
       </c>
@@ -4078,11 +4087,11 @@
       </c>
       <c r="C15" s="4"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>28</v>
       </c>
@@ -4111,7 +4120,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>28</v>
       </c>
@@ -4134,11 +4143,11 @@
         <v>382</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>31</v>
       </c>
@@ -4176,19 +4185,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:O31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>176</v>
       </c>
@@ -4235,7 +4244,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>190</v>
       </c>
@@ -4270,7 +4279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>45</v>
       </c>
@@ -4302,7 +4311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>47</v>
       </c>
@@ -4334,7 +4343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>197</v>
       </c>
@@ -4369,7 +4378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>200</v>
       </c>
@@ -4404,7 +4413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>202</v>
       </c>
@@ -4439,7 +4448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>206</v>
       </c>
@@ -4464,7 +4473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>208</v>
       </c>
@@ -4489,7 +4498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>209</v>
       </c>
@@ -4524,7 +4533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>210</v>
       </c>
@@ -4559,7 +4568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>213</v>
       </c>
@@ -4594,7 +4603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>77</v>
       </c>
@@ -4629,7 +4638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>215</v>
       </c>
@@ -4664,7 +4673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>218</v>
       </c>
@@ -4699,7 +4708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>221</v>
       </c>
@@ -4734,7 +4743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>224</v>
       </c>
@@ -4769,7 +4778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>225</v>
       </c>
@@ -4804,7 +4813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>227</v>
       </c>
@@ -4839,7 +4848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>229</v>
       </c>
@@ -4877,7 +4886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>234</v>
       </c>
@@ -4906,7 +4915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>236</v>
       </c>
@@ -4941,7 +4950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>240</v>
       </c>
@@ -4972,7 +4981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>243</v>
       </c>
@@ -5007,7 +5016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>57</v>
       </c>
@@ -5027,7 +5036,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>376</v>
       </c>
@@ -5053,7 +5062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>245</v>
       </c>
@@ -5079,7 +5088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>246</v>
       </c>
@@ -5108,7 +5117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>248</v>
       </c>
@@ -5137,7 +5146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>250</v>
       </c>
@@ -5177,13 +5186,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
         <v>112</v>
@@ -5200,7 +5209,7 @@
       <c r="I1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>115</v>
       </c>
@@ -5241,7 +5250,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>125</v>
       </c>
@@ -5267,7 +5276,7 @@
         <v>-18877.708702820371</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>131</v>
       </c>
@@ -5293,7 +5302,7 @@
         <v>-19045.139985898601</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>133</v>
       </c>
@@ -5319,7 +5328,7 @@
         <v>-5.4445188599886638</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>135</v>
       </c>
@@ -5345,7 +5354,7 @@
         <v>2.671411511624413</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>137</v>
       </c>
@@ -5371,7 +5380,7 @@
         <v>9.5532474786010475</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -5397,7 +5406,7 @@
         <v>2866.0938229725748</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>131</v>
       </c>
@@ -5423,7 +5432,7 @@
         <v>1490.761502865475</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -5449,7 +5458,7 @@
         <v>2.217459469264154</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -5475,7 +5484,7 @@
         <v>0.2337935274525294</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>137</v>
       </c>
@@ -5501,7 +5510,7 @@
         <v>2.0873115011979051E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>125</v>
       </c>
@@ -5527,7 +5536,7 @@
         <v>1351.711647219304</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>131</v>
       </c>
@@ -5553,7 +5562,7 @@
         <v>150.9391394665019</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>133</v>
       </c>
@@ -5579,7 +5588,7 @@
         <v>1.940117188288828</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>135</v>
       </c>
@@ -5605,7 +5614,7 @@
         <v>-2.0146865510893688E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>137</v>
       </c>
@@ -5638,23 +5647,23 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -5677,7 +5686,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>12</v>
       </c>
@@ -5697,7 +5706,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>12</v>
       </c>
@@ -5714,7 +5723,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>12</v>
       </c>
@@ -5731,7 +5740,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>12</v>
       </c>
@@ -5748,7 +5757,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>12</v>
       </c>
@@ -5765,7 +5774,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>12</v>
       </c>
@@ -5782,7 +5791,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>12</v>
       </c>
@@ -5799,7 +5808,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>15</v>
       </c>
@@ -5816,7 +5825,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
@@ -5833,7 +5842,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>15</v>
       </c>
@@ -5850,7 +5859,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>15</v>
       </c>
@@ -5867,7 +5876,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>15</v>
       </c>
@@ -5884,7 +5893,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="18" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>15</v>
       </c>
@@ -5901,7 +5910,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="19" spans="2:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>15</v>
       </c>
@@ -5918,7 +5927,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>18</v>
       </c>
@@ -5935,7 +5944,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>18</v>
       </c>
@@ -5952,7 +5961,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>18</v>
       </c>
@@ -5969,7 +5978,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>18</v>
       </c>
@@ -5986,7 +5995,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>18</v>
       </c>
@@ -6003,7 +6012,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>18</v>
       </c>
@@ -6020,7 +6029,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>18</v>
       </c>
@@ -6037,29 +6046,29 @@
         <v>159</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>402</v>
       </c>
       <c r="D27">
         <v>1585</v>
       </c>
       <c r="E27">
-        <v>1826</v>
+        <v>2158</v>
       </c>
       <c r="F27" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D28">
         <v>1585</v>
@@ -6071,250 +6080,284 @@
         <v>159</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D29">
+        <v>1585</v>
+      </c>
+      <c r="E29">
         <v>1826</v>
-      </c>
-      <c r="E29">
-        <v>1878</v>
       </c>
       <c r="F29" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D30">
+        <v>1826</v>
+      </c>
+      <c r="E30">
         <v>1878</v>
-      </c>
-      <c r="E30">
-        <v>1984</v>
       </c>
       <c r="F30" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D31">
+        <v>1878</v>
+      </c>
+      <c r="E31">
         <v>1984</v>
-      </c>
-      <c r="E31">
-        <v>2158</v>
       </c>
       <c r="F31" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>28</v>
       </c>
       <c r="C32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D32">
+        <v>1984</v>
+      </c>
+      <c r="E32">
         <v>2158</v>
-      </c>
-      <c r="E32">
-        <v>2211</v>
       </c>
       <c r="F32" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>139</v>
+        <v>404</v>
       </c>
       <c r="D33">
-        <v>2211</v>
+        <v>2158</v>
       </c>
       <c r="E33">
         <v>2365</v>
       </c>
       <c r="F33" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" t="s">
+        <v>164</v>
+      </c>
+      <c r="D34">
+        <v>2158</v>
+      </c>
+      <c r="E34">
+        <v>2211</v>
+      </c>
+      <c r="F34" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="D34" s="30">
-        <v>867.15599999999995</v>
-      </c>
-      <c r="E34" s="30">
-        <v>984.50400000000002</v>
-      </c>
-      <c r="F34" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="D35" s="30">
-        <v>984.50400000000002</v>
-      </c>
-      <c r="E35" s="30">
-        <v>1136.904</v>
+        <v>28</v>
+      </c>
+      <c r="C35" t="s">
+        <v>139</v>
+      </c>
+      <c r="D35">
+        <v>2211</v>
+      </c>
+      <c r="E35">
+        <v>2365</v>
       </c>
       <c r="F35" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>31</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D36" s="30">
-        <v>1136.904</v>
+        <v>867.15599999999995</v>
       </c>
       <c r="E36" s="30">
-        <v>2251.2530000000002</v>
+        <v>984.50400000000002</v>
       </c>
       <c r="F36" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>31</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D37" s="30">
-        <v>2251.2530000000002</v>
+        <v>984.50400000000002</v>
       </c>
       <c r="E37" s="30">
-        <v>2469.2069999999999</v>
+        <v>1136.904</v>
       </c>
       <c r="F37" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>31</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D38" s="30">
-        <v>2469.2069999999999</v>
+        <v>1136.904</v>
       </c>
       <c r="E38" s="30">
-        <v>3190.6460000000002</v>
+        <v>2251.2530000000002</v>
       </c>
       <c r="F38" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>31</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D39" s="30">
-        <v>3190.6460000000002</v>
+        <v>2251.2530000000002</v>
       </c>
       <c r="E39" s="30">
-        <v>3404.3110000000001</v>
+        <v>2469.2069999999999</v>
       </c>
       <c r="F39" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>31</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D40" s="30">
-        <v>3404.3110000000001</v>
+        <v>2469.2069999999999</v>
       </c>
       <c r="E40" s="30">
-        <v>3485.0830000000001</v>
+        <v>3190.6460000000002</v>
       </c>
       <c r="F40" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>31</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D41" s="30">
-        <v>3485.0830000000001</v>
+        <v>3190.6460000000002</v>
       </c>
       <c r="E41" s="30">
-        <v>3964.5340000000001</v>
+        <v>3404.3110000000001</v>
       </c>
       <c r="F41" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>31</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D42" s="30">
-        <v>3964.5340000000001</v>
+        <v>3404.3110000000001</v>
       </c>
       <c r="E42" s="30">
-        <v>4200</v>
+        <v>3485.0830000000001</v>
       </c>
       <c r="F42" t="s">
         <v>166</v>
       </c>
     </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="D43" s="30">
+        <v>3485.0830000000001</v>
+      </c>
+      <c r="E43" s="30">
+        <v>3964.5340000000001</v>
+      </c>
+      <c r="F43" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="D44" s="30">
+        <v>3964.5340000000001</v>
+      </c>
+      <c r="E44" s="30">
+        <v>4200</v>
+      </c>
+      <c r="F44" t="s">
+        <v>166</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations xWindow="120" yWindow="516" count="2">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" prompt="Select well name from &quot;Well settings&quot; sheet" sqref="B44" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" prompt="Select well name from &quot;Well settings&quot; sheet" sqref="B46" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>WellNames</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" error="Only valid well names from &quot;Well settings&quot;" prompt="Select well name from &quot;Well settings&quot; sheet" sqref="B6:B43" xr:uid="{00000000-0002-0000-0500-000001000000}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" error="Only valid well names from &quot;Well settings&quot;" prompt="Select well name from &quot;Well settings&quot; sheet" sqref="B6:B45" xr:uid="{00000000-0002-0000-0500-000001000000}">
       <formula1>WellNames</formula1>
     </dataValidation>
   </dataValidations>
@@ -6325,20 +6368,20 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DE0C751-ACC1-462A-82AF-4CE9BB91C06B}">
-  <dimension ref="A2:G21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:G23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -6361,7 +6404,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -6375,7 +6418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -6389,7 +6432,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -6403,7 +6446,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -6417,7 +6460,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -6431,7 +6474,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -6445,7 +6488,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -6459,7 +6502,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -6473,7 +6516,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -6487,7 +6530,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -6501,7 +6544,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -6515,7 +6558,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -6529,7 +6572,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -6543,7 +6586,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -6557,7 +6600,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -6571,7 +6614,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -6585,8 +6628,36 @@
         <v>19</v>
       </c>
     </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>402</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>404</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="F23" s="24" t="s">
+        <v>220</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A6:A22">
+  <conditionalFormatting sqref="A6:A23">
     <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
@@ -6601,25 +6672,25 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" customWidth="1"/>
-    <col min="7" max="7" width="6.5546875" customWidth="1"/>
-    <col min="8" max="8" width="8.33203125" customWidth="1"/>
-    <col min="9" max="9" width="5.5546875" customWidth="1"/>
-    <col min="10" max="10" width="6.5546875" customWidth="1"/>
-    <col min="11" max="11" width="6.109375" customWidth="1"/>
-    <col min="12" max="12" width="5.109375" customWidth="1"/>
-    <col min="13" max="13" width="5.5546875" customWidth="1"/>
-    <col min="14" max="14" width="5.109375" customWidth="1"/>
-    <col min="15" max="15" width="4.44140625" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" customWidth="1"/>
+    <col min="7" max="7" width="6.5703125" customWidth="1"/>
+    <col min="8" max="8" width="8.28515625" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" customWidth="1"/>
+    <col min="10" max="10" width="6.5703125" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" customWidth="1"/>
+    <col min="13" max="13" width="5.5703125" customWidth="1"/>
+    <col min="14" max="14" width="5.140625" customWidth="1"/>
+    <col min="15" max="15" width="4.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>253</v>
       </c>
@@ -6627,7 +6698,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="8" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" s="8" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>254</v>
       </c>
@@ -6674,7 +6745,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>269</v>
       </c>
@@ -6714,7 +6785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>272</v>
       </c>
@@ -6729,7 +6800,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>394</v>
       </c>
@@ -6769,7 +6840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>400</v>
       </c>
@@ -6785,11 +6856,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
@@ -6811,13 +6882,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="10.33203125" customWidth="1"/>
-    <col min="5" max="6" width="8.5546875" customWidth="1"/>
+    <col min="2" max="4" width="10.28515625" customWidth="1"/>
+    <col min="5" max="6" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6828,7 +6899,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="8" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" s="8" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -6854,7 +6925,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
         <v>21</v>
       </c>
@@ -6870,7 +6941,7 @@
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -6896,7 +6967,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -6922,7 +6993,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="31" t="s">
         <v>21</v>
       </c>
@@ -6948,7 +7019,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -6974,7 +7045,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -7000,7 +7071,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="31" t="s">
         <v>11</v>
       </c>
@@ -7026,7 +7097,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -7052,7 +7123,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -7078,7 +7149,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="31" t="s">
         <v>11</v>
       </c>
@@ -7104,7 +7175,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -7130,7 +7201,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -7156,7 +7227,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="31" t="s">
         <v>11</v>
       </c>
@@ -7182,7 +7253,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -7208,7 +7279,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -7234,7 +7305,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="31" t="s">
         <v>11</v>
       </c>
@@ -7260,7 +7331,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H21" t="s">
         <v>284</v>
       </c>
